--- a/Дело3а-78-2026Таганай/01_Иск/01.9_Прочее_процессуальное/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.9_Прочее_процессуальное/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92536911083</v>
+        <v>46157.93110277196</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.9_Прочее_процессуальное/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.9_Прочее_процессуальное/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93110277196</v>
+        <v>46157.9336571794</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.9_Прочее_процессуальное/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.9_Прочее_процессуальное/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9336571794</v>
+        <v>46157.93667766053</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.9_Прочее_процессуальное/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.9_Прочее_процессуальное/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93667766053</v>
+        <v>46158.28192255514</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.9_Прочее_процессуальное/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.9_Прочее_процессуальное/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28192255514</v>
+        <v>46158.29713134622</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.9_Прочее_процессуальное/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.9_Прочее_процессуальное/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29713134622</v>
+        <v>46158.29787497807</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.9_Прочее_процессуальное/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.9_Прочее_процессуальное/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29787497807</v>
+        <v>46158.33353622467</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.9_Прочее_процессуальное/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.9_Прочее_процессуальное/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33353622467</v>
+        <v>46158.37209388908</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.9_Прочее_процессуальное/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.9_Прочее_процессуальное/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37209388908</v>
+        <v>46158.37428163811</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
